--- a/task6/channelmembers.xlsx
+++ b/task6/channelmembers.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Dropbox\School\6_GT-OMSCS\3_F25\2025-NSA-CBC\task6\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\devel\nsa-cbc-2025\task6\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{30EB5CF2-50BE-4E43-8D85-B89804B50671}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FFA78A4B-0A19-4AFF-8E85-95F3457A8F18}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-30828" yWindow="-204" windowWidth="30936" windowHeight="16776" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="30936" windowHeight="16776" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -510,7 +510,7 @@
         <v>33</v>
       </c>
       <c r="B2" t="s">
-        <v>20</v>
+        <v>36</v>
       </c>
       <c r="C2">
         <v>0</v>
@@ -518,10 +518,10 @@
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
-        <v>33</v>
+        <v>7</v>
       </c>
       <c r="B3" t="s">
-        <v>21</v>
+        <v>36</v>
       </c>
       <c r="C3">
         <v>0</v>
@@ -529,10 +529,10 @@
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
-        <v>33</v>
+        <v>38</v>
       </c>
       <c r="B4" t="s">
-        <v>12</v>
+        <v>36</v>
       </c>
       <c r="C4">
         <v>0</v>
@@ -540,10 +540,10 @@
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
-        <v>33</v>
+        <v>4</v>
       </c>
       <c r="B5" t="s">
-        <v>18</v>
+        <v>36</v>
       </c>
       <c r="C5">
         <v>0</v>
@@ -551,10 +551,10 @@
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
-        <v>33</v>
+        <v>40</v>
       </c>
       <c r="B6" t="s">
-        <v>16</v>
+        <v>36</v>
       </c>
       <c r="C6">
         <v>0</v>
@@ -562,10 +562,10 @@
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
-        <v>33</v>
+        <v>41</v>
       </c>
       <c r="B7" t="s">
-        <v>10</v>
+        <v>36</v>
       </c>
       <c r="C7">
         <v>0</v>
@@ -573,10 +573,10 @@
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
-        <v>33</v>
+        <v>2</v>
       </c>
       <c r="B8" t="s">
-        <v>29</v>
+        <v>36</v>
       </c>
       <c r="C8">
         <v>0</v>
@@ -584,29 +584,29 @@
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
-        <v>33</v>
+        <v>25</v>
       </c>
       <c r="B9" t="s">
-        <v>9</v>
+        <v>36</v>
       </c>
       <c r="C9">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
-        <v>33</v>
+        <v>22</v>
       </c>
       <c r="B10" t="s">
-        <v>24</v>
+        <v>36</v>
       </c>
       <c r="C10">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
-        <v>33</v>
+        <v>0</v>
       </c>
       <c r="B11" t="s">
         <v>36</v>
@@ -617,10 +617,10 @@
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
-        <v>33</v>
+        <v>19</v>
       </c>
       <c r="B12" t="s">
-        <v>15</v>
+        <v>36</v>
       </c>
       <c r="C12">
         <v>0</v>
@@ -628,21 +628,21 @@
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="B13" t="s">
-        <v>1</v>
+        <v>36</v>
       </c>
       <c r="C13">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
-        <v>7</v>
+        <v>31</v>
       </c>
       <c r="B14" t="s">
-        <v>15</v>
+        <v>36</v>
       </c>
       <c r="C14">
         <v>0</v>
@@ -650,10 +650,10 @@
     </row>
     <row r="15" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
-        <v>7</v>
+        <v>35</v>
       </c>
       <c r="B15" t="s">
-        <v>20</v>
+        <v>36</v>
       </c>
       <c r="C15">
         <v>0</v>
@@ -661,10 +661,10 @@
     </row>
     <row r="16" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
-        <v>7</v>
+        <v>34</v>
       </c>
       <c r="B16" t="s">
-        <v>21</v>
+        <v>36</v>
       </c>
       <c r="C16">
         <v>0</v>
@@ -672,10 +672,10 @@
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
-        <v>7</v>
+        <v>27</v>
       </c>
       <c r="B17" t="s">
-        <v>11</v>
+        <v>36</v>
       </c>
       <c r="C17">
         <v>0</v>
@@ -683,10 +683,10 @@
     </row>
     <row r="18" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
-        <v>7</v>
+        <v>28</v>
       </c>
       <c r="B18" t="s">
-        <v>12</v>
+        <v>36</v>
       </c>
       <c r="C18">
         <v>0</v>
@@ -694,10 +694,10 @@
     </row>
     <row r="19" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="B19" t="s">
-        <v>23</v>
+        <v>36</v>
       </c>
       <c r="C19">
         <v>0</v>
@@ -705,10 +705,10 @@
     </row>
     <row r="20" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="B20" t="s">
-        <v>26</v>
+        <v>36</v>
       </c>
       <c r="C20">
         <v>0</v>
@@ -716,10 +716,10 @@
     </row>
     <row r="21" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
-        <v>7</v>
+        <v>37</v>
       </c>
       <c r="B21" t="s">
-        <v>16</v>
+        <v>36</v>
       </c>
       <c r="C21">
         <v>0</v>
@@ -727,10 +727,10 @@
     </row>
     <row r="22" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
-        <v>7</v>
+        <v>30</v>
       </c>
       <c r="B22" t="s">
-        <v>24</v>
+        <v>36</v>
       </c>
       <c r="C22">
         <v>0</v>
@@ -738,10 +738,10 @@
     </row>
     <row r="23" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
-        <v>7</v>
+        <v>17</v>
       </c>
       <c r="B23" t="s">
-        <v>9</v>
+        <v>36</v>
       </c>
       <c r="C23">
         <v>0</v>
@@ -749,10 +749,10 @@
     </row>
     <row r="24" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
-        <v>7</v>
+        <v>32</v>
       </c>
       <c r="B24" t="s">
-        <v>29</v>
+        <v>36</v>
       </c>
       <c r="C24">
         <v>0</v>
@@ -760,7 +760,7 @@
     </row>
     <row r="25" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
-        <v>7</v>
+        <v>39</v>
       </c>
       <c r="B25" t="s">
         <v>36</v>
@@ -771,21 +771,21 @@
     </row>
     <row r="26" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="B26" t="s">
-        <v>3</v>
+        <v>36</v>
       </c>
       <c r="C26">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="27" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
-        <v>7</v>
+        <v>33</v>
       </c>
       <c r="B27" t="s">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="C27">
         <v>0</v>
@@ -793,10 +793,10 @@
     </row>
     <row r="28" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
-        <v>38</v>
+        <v>7</v>
       </c>
       <c r="B28" t="s">
-        <v>6</v>
+        <v>15</v>
       </c>
       <c r="C28">
         <v>0</v>
@@ -804,10 +804,10 @@
     </row>
     <row r="29" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
-        <v>38</v>
+        <v>4</v>
       </c>
       <c r="B29" t="s">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="C29">
         <v>0</v>
@@ -815,10 +815,10 @@
     </row>
     <row r="30" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="B30" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="C30">
         <v>0</v>
@@ -826,10 +826,10 @@
     </row>
     <row r="31" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="B31" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="C31">
         <v>0</v>
@@ -837,10 +837,10 @@
     </row>
     <row r="32" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
-        <v>38</v>
+        <v>2</v>
       </c>
       <c r="B32" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="C32">
         <v>0</v>
@@ -848,10 +848,10 @@
     </row>
     <row r="33" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A33" t="s">
-        <v>38</v>
+        <v>25</v>
       </c>
       <c r="B33" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="C33">
         <v>0</v>
@@ -859,10 +859,10 @@
     </row>
     <row r="34" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A34" t="s">
-        <v>38</v>
+        <v>22</v>
       </c>
       <c r="B34" t="s">
-        <v>26</v>
+        <v>15</v>
       </c>
       <c r="C34">
         <v>0</v>
@@ -870,10 +870,10 @@
     </row>
     <row r="35" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A35" t="s">
-        <v>38</v>
+        <v>0</v>
       </c>
       <c r="B35" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C35">
         <v>0</v>
@@ -881,10 +881,10 @@
     </row>
     <row r="36" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A36" t="s">
-        <v>38</v>
+        <v>19</v>
       </c>
       <c r="B36" t="s">
-        <v>36</v>
+        <v>15</v>
       </c>
       <c r="C36">
         <v>0</v>
@@ -892,10 +892,10 @@
     </row>
     <row r="37" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A37" t="s">
-        <v>38</v>
+        <v>13</v>
       </c>
       <c r="B37" t="s">
-        <v>24</v>
+        <v>15</v>
       </c>
       <c r="C37">
         <v>0</v>
@@ -903,10 +903,10 @@
     </row>
     <row r="38" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A38" t="s">
-        <v>38</v>
+        <v>31</v>
       </c>
       <c r="B38" t="s">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="C38">
         <v>0</v>
@@ -914,10 +914,10 @@
     </row>
     <row r="39" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A39" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="B39" t="s">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="C39">
         <v>0</v>
@@ -925,10 +925,10 @@
     </row>
     <row r="40" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A40" t="s">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="B40" t="s">
-        <v>29</v>
+        <v>15</v>
       </c>
       <c r="C40">
         <v>0</v>
@@ -936,43 +936,43 @@
     </row>
     <row r="41" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A41" t="s">
-        <v>38</v>
+        <v>28</v>
       </c>
       <c r="B41" t="s">
-        <v>3</v>
+        <v>15</v>
       </c>
       <c r="C41">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="42" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A42" t="s">
-        <v>38</v>
+        <v>14</v>
       </c>
       <c r="B42" t="s">
-        <v>1</v>
+        <v>15</v>
       </c>
       <c r="C42">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="43" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A43" t="s">
-        <v>4</v>
+        <v>30</v>
       </c>
       <c r="B43" t="s">
-        <v>1</v>
+        <v>15</v>
       </c>
       <c r="C43">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="44" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A44" t="s">
-        <v>4</v>
+        <v>17</v>
       </c>
       <c r="B44" t="s">
-        <v>36</v>
+        <v>15</v>
       </c>
       <c r="C44">
         <v>0</v>
@@ -980,7 +980,7 @@
     </row>
     <row r="45" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A45" t="s">
-        <v>4</v>
+        <v>32</v>
       </c>
       <c r="B45" t="s">
         <v>15</v>
@@ -991,10 +991,10 @@
     </row>
     <row r="46" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A46" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="B46" t="s">
-        <v>6</v>
+        <v>15</v>
       </c>
       <c r="C46">
         <v>0</v>
@@ -1002,10 +1002,10 @@
     </row>
     <row r="47" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A47" t="s">
-        <v>4</v>
+        <v>38</v>
       </c>
       <c r="B47" t="s">
-        <v>20</v>
+        <v>6</v>
       </c>
       <c r="C47">
         <v>0</v>
@@ -1016,7 +1016,7 @@
         <v>4</v>
       </c>
       <c r="B48" t="s">
-        <v>21</v>
+        <v>6</v>
       </c>
       <c r="C48">
         <v>0</v>
@@ -1024,10 +1024,10 @@
     </row>
     <row r="49" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A49" t="s">
-        <v>4</v>
+        <v>40</v>
       </c>
       <c r="B49" t="s">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="C49">
         <v>0</v>
@@ -1035,10 +1035,10 @@
     </row>
     <row r="50" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A50" t="s">
-        <v>4</v>
+        <v>41</v>
       </c>
       <c r="B50" t="s">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="C50">
         <v>0</v>
@@ -1046,10 +1046,10 @@
     </row>
     <row r="51" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A51" t="s">
-        <v>4</v>
+        <v>25</v>
       </c>
       <c r="B51" t="s">
-        <v>18</v>
+        <v>6</v>
       </c>
       <c r="C51">
         <v>0</v>
@@ -1057,10 +1057,10 @@
     </row>
     <row r="52" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A52" t="s">
-        <v>4</v>
+        <v>22</v>
       </c>
       <c r="B52" t="s">
-        <v>24</v>
+        <v>6</v>
       </c>
       <c r="C52">
         <v>0</v>
@@ -1068,10 +1068,10 @@
     </row>
     <row r="53" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A53" t="s">
-        <v>4</v>
+        <v>19</v>
       </c>
       <c r="B53" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="C53">
         <v>0</v>
@@ -1079,10 +1079,10 @@
     </row>
     <row r="54" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A54" t="s">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="B54" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="C54">
         <v>0</v>
@@ -1090,10 +1090,10 @@
     </row>
     <row r="55" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A55" t="s">
-        <v>4</v>
+        <v>31</v>
       </c>
       <c r="B55" t="s">
-        <v>29</v>
+        <v>6</v>
       </c>
       <c r="C55">
         <v>0</v>
@@ -1101,21 +1101,21 @@
     </row>
     <row r="56" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A56" t="s">
-        <v>4</v>
+        <v>34</v>
       </c>
       <c r="B56" t="s">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="C56">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="57" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A57" t="s">
-        <v>4</v>
+        <v>27</v>
       </c>
       <c r="B57" t="s">
-        <v>16</v>
+        <v>6</v>
       </c>
       <c r="C57">
         <v>0</v>
@@ -1123,29 +1123,29 @@
     </row>
     <row r="58" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A58" t="s">
-        <v>40</v>
+        <v>28</v>
       </c>
       <c r="B58" t="s">
-        <v>36</v>
+        <v>6</v>
       </c>
       <c r="C58">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="59" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A59" t="s">
-        <v>40</v>
+        <v>5</v>
       </c>
       <c r="B59" t="s">
-        <v>15</v>
+        <v>6</v>
       </c>
       <c r="C59">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="60" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A60" t="s">
-        <v>40</v>
+        <v>14</v>
       </c>
       <c r="B60" t="s">
         <v>6</v>
@@ -1156,10 +1156,10 @@
     </row>
     <row r="61" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A61" t="s">
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="B61" t="s">
-        <v>21</v>
+        <v>6</v>
       </c>
       <c r="C61">
         <v>0</v>
@@ -1167,21 +1167,21 @@
     </row>
     <row r="62" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A62" t="s">
-        <v>40</v>
+        <v>32</v>
       </c>
       <c r="B62" t="s">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="C62">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="63" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A63" t="s">
-        <v>40</v>
+        <v>8</v>
       </c>
       <c r="B63" t="s">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="C63">
         <v>0</v>
@@ -1189,10 +1189,10 @@
     </row>
     <row r="64" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A64" t="s">
-        <v>40</v>
+        <v>33</v>
       </c>
       <c r="B64" t="s">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="C64">
         <v>0</v>
@@ -1200,10 +1200,10 @@
     </row>
     <row r="65" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A65" t="s">
-        <v>40</v>
+        <v>7</v>
       </c>
       <c r="B65" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="C65">
         <v>0</v>
@@ -1211,10 +1211,10 @@
     </row>
     <row r="66" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A66" t="s">
-        <v>40</v>
+        <v>4</v>
       </c>
       <c r="B66" t="s">
-        <v>26</v>
+        <v>20</v>
       </c>
       <c r="C66">
         <v>0</v>
@@ -1222,10 +1222,10 @@
     </row>
     <row r="67" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A67" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B67" t="s">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="C67">
         <v>0</v>
@@ -1233,10 +1233,10 @@
     </row>
     <row r="68" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A68" t="s">
-        <v>40</v>
+        <v>2</v>
       </c>
       <c r="B68" t="s">
-        <v>9</v>
+        <v>20</v>
       </c>
       <c r="C68">
         <v>0</v>
@@ -1244,10 +1244,10 @@
     </row>
     <row r="69" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A69" t="s">
-        <v>40</v>
+        <v>25</v>
       </c>
       <c r="B69" t="s">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="C69">
         <v>0</v>
@@ -1255,10 +1255,10 @@
     </row>
     <row r="70" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A70" t="s">
-        <v>40</v>
+        <v>22</v>
       </c>
       <c r="B70" t="s">
-        <v>29</v>
+        <v>20</v>
       </c>
       <c r="C70">
         <v>0</v>
@@ -1266,32 +1266,32 @@
     </row>
     <row r="71" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A71" t="s">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="B71" t="s">
-        <v>3</v>
+        <v>20</v>
       </c>
       <c r="C71">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="72" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A72" t="s">
-        <v>40</v>
+        <v>19</v>
       </c>
       <c r="B72" t="s">
-        <v>1</v>
+        <v>20</v>
       </c>
       <c r="C72">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="73" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A73" t="s">
-        <v>41</v>
+        <v>13</v>
       </c>
       <c r="B73" t="s">
-        <v>36</v>
+        <v>20</v>
       </c>
       <c r="C73">
         <v>0</v>
@@ -1299,10 +1299,10 @@
     </row>
     <row r="74" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A74" t="s">
-        <v>41</v>
+        <v>35</v>
       </c>
       <c r="B74" t="s">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="C74">
         <v>0</v>
@@ -1310,10 +1310,10 @@
     </row>
     <row r="75" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A75" t="s">
-        <v>41</v>
+        <v>34</v>
       </c>
       <c r="B75" t="s">
-        <v>6</v>
+        <v>20</v>
       </c>
       <c r="C75">
         <v>0</v>
@@ -1321,10 +1321,10 @@
     </row>
     <row r="76" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A76" t="s">
-        <v>41</v>
+        <v>27</v>
       </c>
       <c r="B76" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="C76">
         <v>0</v>
@@ -1332,10 +1332,10 @@
     </row>
     <row r="77" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A77" t="s">
-        <v>41</v>
+        <v>28</v>
       </c>
       <c r="B77" t="s">
-        <v>11</v>
+        <v>20</v>
       </c>
       <c r="C77">
         <v>0</v>
@@ -1343,10 +1343,10 @@
     </row>
     <row r="78" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A78" t="s">
-        <v>41</v>
+        <v>5</v>
       </c>
       <c r="B78" t="s">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="C78">
         <v>0</v>
@@ -1354,10 +1354,10 @@
     </row>
     <row r="79" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A79" t="s">
-        <v>41</v>
+        <v>14</v>
       </c>
       <c r="B79" t="s">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="C79">
         <v>0</v>
@@ -1365,10 +1365,10 @@
     </row>
     <row r="80" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A80" t="s">
-        <v>41</v>
+        <v>30</v>
       </c>
       <c r="B80" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="C80">
         <v>0</v>
@@ -1376,10 +1376,10 @@
     </row>
     <row r="81" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A81" t="s">
-        <v>41</v>
+        <v>17</v>
       </c>
       <c r="B81" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="C81">
         <v>0</v>
@@ -1387,10 +1387,10 @@
     </row>
     <row r="82" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A82" t="s">
-        <v>41</v>
+        <v>32</v>
       </c>
       <c r="B82" t="s">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="C82">
         <v>0</v>
@@ -1398,21 +1398,21 @@
     </row>
     <row r="83" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A83" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="B83" t="s">
-        <v>9</v>
+        <v>20</v>
       </c>
       <c r="C83">
-        <v>0</v>
+        <v>37</v>
       </c>
     </row>
     <row r="84" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A84" t="s">
-        <v>41</v>
+        <v>8</v>
       </c>
       <c r="B84" t="s">
-        <v>29</v>
+        <v>20</v>
       </c>
       <c r="C84">
         <v>0</v>
@@ -1420,65 +1420,65 @@
     </row>
     <row r="85" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A85" t="s">
-        <v>41</v>
+        <v>35</v>
       </c>
       <c r="B85" t="s">
-        <v>20</v>
+        <v>42</v>
       </c>
       <c r="C85">
-        <v>0</v>
+        <v>15</v>
       </c>
     </row>
     <row r="86" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A86" t="s">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="B86" t="s">
-        <v>3</v>
+        <v>42</v>
       </c>
       <c r="C86">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="87" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A87" t="s">
-        <v>41</v>
+        <v>33</v>
       </c>
       <c r="B87" t="s">
-        <v>1</v>
+        <v>21</v>
       </c>
       <c r="C87">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="88" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A88" t="s">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="B88" t="s">
-        <v>3</v>
+        <v>21</v>
       </c>
       <c r="C88">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="89" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A89" t="s">
-        <v>2</v>
+        <v>38</v>
       </c>
       <c r="B89" t="s">
-        <v>1</v>
+        <v>21</v>
       </c>
       <c r="C89">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="90" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A90" t="s">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="B90" t="s">
-        <v>36</v>
+        <v>21</v>
       </c>
       <c r="C90">
         <v>0</v>
@@ -1486,10 +1486,10 @@
     </row>
     <row r="91" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A91" t="s">
-        <v>2</v>
+        <v>40</v>
       </c>
       <c r="B91" t="s">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="C91">
         <v>0</v>
@@ -1497,10 +1497,10 @@
     </row>
     <row r="92" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A92" t="s">
-        <v>2</v>
+        <v>41</v>
       </c>
       <c r="B92" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C92">
         <v>0</v>
@@ -1519,10 +1519,10 @@
     </row>
     <row r="94" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A94" t="s">
-        <v>2</v>
+        <v>22</v>
       </c>
       <c r="B94" t="s">
-        <v>11</v>
+        <v>21</v>
       </c>
       <c r="C94">
         <v>0</v>
@@ -1530,10 +1530,10 @@
     </row>
     <row r="95" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A95" t="s">
-        <v>2</v>
+        <v>19</v>
       </c>
       <c r="B95" t="s">
-        <v>12</v>
+        <v>21</v>
       </c>
       <c r="C95">
         <v>0</v>
@@ -1541,10 +1541,10 @@
     </row>
     <row r="96" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A96" t="s">
-        <v>2</v>
+        <v>13</v>
       </c>
       <c r="B96" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="C96">
         <v>0</v>
@@ -1552,10 +1552,10 @@
     </row>
     <row r="97" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A97" t="s">
-        <v>2</v>
+        <v>31</v>
       </c>
       <c r="B97" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="C97">
         <v>0</v>
@@ -1563,10 +1563,10 @@
     </row>
     <row r="98" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A98" t="s">
-        <v>2</v>
+        <v>35</v>
       </c>
       <c r="B98" t="s">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="C98">
         <v>0</v>
@@ -1574,10 +1574,10 @@
     </row>
     <row r="99" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A99" t="s">
-        <v>2</v>
+        <v>34</v>
       </c>
       <c r="B99" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="C99">
         <v>0</v>
@@ -1585,10 +1585,10 @@
     </row>
     <row r="100" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A100" t="s">
-        <v>2</v>
+        <v>27</v>
       </c>
       <c r="B100" t="s">
-        <v>9</v>
+        <v>21</v>
       </c>
       <c r="C100">
         <v>0</v>
@@ -1596,10 +1596,10 @@
     </row>
     <row r="101" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A101" t="s">
-        <v>2</v>
+        <v>28</v>
       </c>
       <c r="B101" t="s">
-        <v>10</v>
+        <v>21</v>
       </c>
       <c r="C101">
         <v>0</v>
@@ -1607,10 +1607,10 @@
     </row>
     <row r="102" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A102" t="s">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="B102" t="s">
-        <v>29</v>
+        <v>21</v>
       </c>
       <c r="C102">
         <v>0</v>
@@ -1618,32 +1618,32 @@
     </row>
     <row r="103" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A103" t="s">
-        <v>25</v>
+        <v>14</v>
       </c>
       <c r="B103" t="s">
-        <v>3</v>
+        <v>21</v>
       </c>
       <c r="C103">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="104" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A104" t="s">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="B104" t="s">
-        <v>1</v>
+        <v>21</v>
       </c>
       <c r="C104">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="105" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A105" t="s">
-        <v>25</v>
+        <v>17</v>
       </c>
       <c r="B105" t="s">
-        <v>10</v>
+        <v>21</v>
       </c>
       <c r="C105">
         <v>0</v>
@@ -1651,10 +1651,10 @@
     </row>
     <row r="106" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A106" t="s">
-        <v>25</v>
+        <v>32</v>
       </c>
       <c r="B106" t="s">
-        <v>36</v>
+        <v>21</v>
       </c>
       <c r="C106">
         <v>0</v>
@@ -1662,10 +1662,10 @@
     </row>
     <row r="107" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A107" t="s">
-        <v>25</v>
+        <v>8</v>
       </c>
       <c r="B107" t="s">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="C107">
         <v>0</v>
@@ -1673,10 +1673,10 @@
     </row>
     <row r="108" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A108" t="s">
-        <v>25</v>
+        <v>7</v>
       </c>
       <c r="B108" t="s">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="C108">
         <v>0</v>
@@ -1684,10 +1684,10 @@
     </row>
     <row r="109" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A109" t="s">
-        <v>25</v>
+        <v>38</v>
       </c>
       <c r="B109" t="s">
-        <v>20</v>
+        <v>11</v>
       </c>
       <c r="C109">
         <v>0</v>
@@ -1695,7 +1695,7 @@
     </row>
     <row r="110" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A110" t="s">
-        <v>25</v>
+        <v>4</v>
       </c>
       <c r="B110" t="s">
         <v>11</v>
@@ -1706,10 +1706,10 @@
     </row>
     <row r="111" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A111" t="s">
-        <v>25</v>
+        <v>40</v>
       </c>
       <c r="B111" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C111">
         <v>0</v>
@@ -1717,10 +1717,10 @@
     </row>
     <row r="112" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A112" t="s">
-        <v>25</v>
+        <v>41</v>
       </c>
       <c r="B112" t="s">
-        <v>23</v>
+        <v>11</v>
       </c>
       <c r="C112">
         <v>0</v>
@@ -1728,10 +1728,10 @@
     </row>
     <row r="113" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A113" t="s">
-        <v>25</v>
+        <v>2</v>
       </c>
       <c r="B113" t="s">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="C113">
         <v>0</v>
@@ -1742,7 +1742,7 @@
         <v>25</v>
       </c>
       <c r="B114" t="s">
-        <v>26</v>
+        <v>11</v>
       </c>
       <c r="C114">
         <v>0</v>
@@ -1750,10 +1750,10 @@
     </row>
     <row r="115" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A115" t="s">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="B115" t="s">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="C115">
         <v>0</v>
@@ -1761,10 +1761,10 @@
     </row>
     <row r="116" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A116" t="s">
-        <v>25</v>
+        <v>19</v>
       </c>
       <c r="B116" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="C116">
         <v>0</v>
@@ -1772,10 +1772,10 @@
     </row>
     <row r="117" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A117" t="s">
-        <v>25</v>
+        <v>13</v>
       </c>
       <c r="B117" t="s">
-        <v>29</v>
+        <v>11</v>
       </c>
       <c r="C117">
         <v>0</v>
@@ -1783,10 +1783,10 @@
     </row>
     <row r="118" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A118" t="s">
-        <v>22</v>
+        <v>31</v>
       </c>
       <c r="B118" t="s">
-        <v>21</v>
+        <v>11</v>
       </c>
       <c r="C118">
         <v>0</v>
@@ -1794,10 +1794,10 @@
     </row>
     <row r="119" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A119" t="s">
-        <v>22</v>
+        <v>35</v>
       </c>
       <c r="B119" t="s">
-        <v>23</v>
+        <v>11</v>
       </c>
       <c r="C119">
         <v>0</v>
@@ -1805,10 +1805,10 @@
     </row>
     <row r="120" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A120" t="s">
-        <v>22</v>
+        <v>27</v>
       </c>
       <c r="B120" t="s">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="C120">
         <v>0</v>
@@ -1816,10 +1816,10 @@
     </row>
     <row r="121" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A121" t="s">
-        <v>22</v>
+        <v>28</v>
       </c>
       <c r="B121" t="s">
-        <v>24</v>
+        <v>11</v>
       </c>
       <c r="C121">
         <v>0</v>
@@ -1827,10 +1827,10 @@
     </row>
     <row r="122" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A122" t="s">
-        <v>22</v>
+        <v>5</v>
       </c>
       <c r="B122" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C122">
         <v>0</v>
@@ -1838,32 +1838,32 @@
     </row>
     <row r="123" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A123" t="s">
-        <v>22</v>
+        <v>14</v>
       </c>
       <c r="B123" t="s">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="C123">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="124" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A124" t="s">
-        <v>22</v>
+        <v>30</v>
       </c>
       <c r="B124" t="s">
-        <v>3</v>
+        <v>11</v>
       </c>
       <c r="C124">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="125" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A125" t="s">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="B125" t="s">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="C125">
         <v>0</v>
@@ -1871,10 +1871,10 @@
     </row>
     <row r="126" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A126" t="s">
-        <v>22</v>
+        <v>32</v>
       </c>
       <c r="B126" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C126">
         <v>0</v>
@@ -1882,21 +1882,21 @@
     </row>
     <row r="127" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A127" t="s">
-        <v>22</v>
+        <v>39</v>
       </c>
       <c r="B127" t="s">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="C127">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="128" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A128" t="s">
-        <v>22</v>
+        <v>8</v>
       </c>
       <c r="B128" t="s">
-        <v>26</v>
+        <v>11</v>
       </c>
       <c r="C128">
         <v>0</v>
@@ -1904,10 +1904,10 @@
     </row>
     <row r="129" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A129" t="s">
-        <v>22</v>
+        <v>33</v>
       </c>
       <c r="B129" t="s">
-        <v>29</v>
+        <v>12</v>
       </c>
       <c r="C129">
         <v>0</v>
@@ -1915,10 +1915,10 @@
     </row>
     <row r="130" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A130" t="s">
-        <v>22</v>
+        <v>7</v>
       </c>
       <c r="B130" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="C130">
         <v>0</v>
@@ -1926,10 +1926,10 @@
     </row>
     <row r="131" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A131" t="s">
-        <v>22</v>
+        <v>38</v>
       </c>
       <c r="B131" t="s">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="C131">
         <v>0</v>
@@ -1937,10 +1937,10 @@
     </row>
     <row r="132" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A132" t="s">
-        <v>22</v>
+        <v>4</v>
       </c>
       <c r="B132" t="s">
-        <v>36</v>
+        <v>12</v>
       </c>
       <c r="C132">
         <v>0</v>
@@ -1948,32 +1948,32 @@
     </row>
     <row r="133" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A133" t="s">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="B133" t="s">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="C133">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="134" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A134" t="s">
-        <v>0</v>
+        <v>41</v>
       </c>
       <c r="B134" t="s">
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="C134">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="135" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A135" t="s">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="B135" t="s">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="C135">
         <v>0</v>
@@ -1981,10 +1981,10 @@
     </row>
     <row r="136" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A136" t="s">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="B136" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="C136">
         <v>0</v>
@@ -1992,10 +1992,10 @@
     </row>
     <row r="137" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A137" t="s">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="B137" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="C137">
         <v>0</v>
@@ -2006,7 +2006,7 @@
         <v>0</v>
       </c>
       <c r="B138" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="C138">
         <v>0</v>
@@ -2014,10 +2014,10 @@
     </row>
     <row r="139" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A139" t="s">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="B139" t="s">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="C139">
         <v>0</v>
@@ -2025,10 +2025,10 @@
     </row>
     <row r="140" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A140" t="s">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="B140" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C140">
         <v>0</v>
@@ -2036,7 +2036,7 @@
     </row>
     <row r="141" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A141" t="s">
-        <v>0</v>
+        <v>31</v>
       </c>
       <c r="B141" t="s">
         <v>12</v>
@@ -2047,10 +2047,10 @@
     </row>
     <row r="142" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A142" t="s">
-        <v>0</v>
+        <v>35</v>
       </c>
       <c r="B142" t="s">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="C142">
         <v>0</v>
@@ -2058,10 +2058,10 @@
     </row>
     <row r="143" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A143" t="s">
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="B143" t="s">
-        <v>26</v>
+        <v>12</v>
       </c>
       <c r="C143">
         <v>0</v>
@@ -2069,10 +2069,10 @@
     </row>
     <row r="144" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A144" t="s">
-        <v>0</v>
+        <v>27</v>
       </c>
       <c r="B144" t="s">
-        <v>29</v>
+        <v>12</v>
       </c>
       <c r="C144">
         <v>0</v>
@@ -2080,10 +2080,10 @@
     </row>
     <row r="145" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A145" t="s">
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="B145" t="s">
-        <v>36</v>
+        <v>12</v>
       </c>
       <c r="C145">
         <v>0</v>
@@ -2091,21 +2091,21 @@
     </row>
     <row r="146" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A146" t="s">
-        <v>19</v>
+        <v>5</v>
       </c>
       <c r="B146" t="s">
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="C146">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="147" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A147" t="s">
-        <v>19</v>
+        <v>30</v>
       </c>
       <c r="B147" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="C147">
         <v>0</v>
@@ -2113,10 +2113,10 @@
     </row>
     <row r="148" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A148" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="B148" t="s">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="C148">
         <v>0</v>
@@ -2124,10 +2124,10 @@
     </row>
     <row r="149" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A149" t="s">
-        <v>19</v>
+        <v>32</v>
       </c>
       <c r="B149" t="s">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="C149">
         <v>0</v>
@@ -2135,21 +2135,21 @@
     </row>
     <row r="150" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A150" t="s">
-        <v>19</v>
+        <v>39</v>
       </c>
       <c r="B150" t="s">
-        <v>21</v>
+        <v>12</v>
       </c>
       <c r="C150">
-        <v>0</v>
+        <v>39</v>
       </c>
     </row>
     <row r="151" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A151" t="s">
-        <v>19</v>
+        <v>7</v>
       </c>
       <c r="B151" t="s">
-        <v>11</v>
+        <v>23</v>
       </c>
       <c r="C151">
         <v>0</v>
@@ -2157,10 +2157,10 @@
     </row>
     <row r="152" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A152" t="s">
-        <v>19</v>
+        <v>38</v>
       </c>
       <c r="B152" t="s">
-        <v>12</v>
+        <v>23</v>
       </c>
       <c r="C152">
         <v>0</v>
@@ -2168,10 +2168,10 @@
     </row>
     <row r="153" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A153" t="s">
-        <v>19</v>
+        <v>40</v>
       </c>
       <c r="B153" t="s">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="C153">
         <v>0</v>
@@ -2179,10 +2179,10 @@
     </row>
     <row r="154" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A154" t="s">
-        <v>19</v>
+        <v>41</v>
       </c>
       <c r="B154" t="s">
-        <v>9</v>
+        <v>23</v>
       </c>
       <c r="C154">
         <v>0</v>
@@ -2190,10 +2190,10 @@
     </row>
     <row r="155" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A155" t="s">
-        <v>19</v>
+        <v>2</v>
       </c>
       <c r="B155" t="s">
-        <v>10</v>
+        <v>23</v>
       </c>
       <c r="C155">
         <v>0</v>
@@ -2201,10 +2201,10 @@
     </row>
     <row r="156" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A156" t="s">
-        <v>19</v>
+        <v>25</v>
       </c>
       <c r="B156" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="C156">
         <v>0</v>
@@ -2212,10 +2212,10 @@
     </row>
     <row r="157" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A157" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="B157" t="s">
-        <v>16</v>
+        <v>23</v>
       </c>
       <c r="C157">
         <v>0</v>
@@ -2223,10 +2223,10 @@
     </row>
     <row r="158" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A158" t="s">
-        <v>19</v>
+        <v>31</v>
       </c>
       <c r="B158" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C158">
         <v>0</v>
@@ -2234,10 +2234,10 @@
     </row>
     <row r="159" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A159" t="s">
-        <v>19</v>
+        <v>35</v>
       </c>
       <c r="B159" t="s">
-        <v>36</v>
+        <v>23</v>
       </c>
       <c r="C159">
         <v>0</v>
@@ -2245,21 +2245,21 @@
     </row>
     <row r="160" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A160" t="s">
-        <v>19</v>
+        <v>34</v>
       </c>
       <c r="B160" t="s">
-        <v>1</v>
+        <v>23</v>
       </c>
       <c r="C160">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="161" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A161" t="s">
-        <v>13</v>
+        <v>27</v>
       </c>
       <c r="B161" t="s">
-        <v>11</v>
+        <v>23</v>
       </c>
       <c r="C161">
         <v>0</v>
@@ -2267,10 +2267,10 @@
     </row>
     <row r="162" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A162" t="s">
-        <v>13</v>
+        <v>28</v>
       </c>
       <c r="B162" t="s">
-        <v>6</v>
+        <v>23</v>
       </c>
       <c r="C162">
         <v>0</v>
@@ -2278,10 +2278,10 @@
     </row>
     <row r="163" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A163" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B163" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="C163">
         <v>0</v>
@@ -2289,10 +2289,10 @@
     </row>
     <row r="164" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A164" t="s">
-        <v>13</v>
+        <v>30</v>
       </c>
       <c r="B164" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="C164">
         <v>0</v>
@@ -2300,10 +2300,10 @@
     </row>
     <row r="165" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A165" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B165" t="s">
-        <v>12</v>
+        <v>23</v>
       </c>
       <c r="C165">
         <v>0</v>
@@ -2311,10 +2311,10 @@
     </row>
     <row r="166" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A166" t="s">
-        <v>13</v>
+        <v>32</v>
       </c>
       <c r="B166" t="s">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="C166">
         <v>0</v>
@@ -2322,10 +2322,10 @@
     </row>
     <row r="167" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A167" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="B167" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="C167">
         <v>0</v>
@@ -2333,10 +2333,10 @@
     </row>
     <row r="168" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A168" t="s">
-        <v>13</v>
+        <v>33</v>
       </c>
       <c r="B168" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="C168">
         <v>0</v>
@@ -2344,10 +2344,10 @@
     </row>
     <row r="169" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A169" t="s">
-        <v>13</v>
+        <v>38</v>
       </c>
       <c r="B169" t="s">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="C169">
         <v>0</v>
@@ -2355,10 +2355,10 @@
     </row>
     <row r="170" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A170" t="s">
-        <v>13</v>
+        <v>4</v>
       </c>
       <c r="B170" t="s">
-        <v>10</v>
+        <v>18</v>
       </c>
       <c r="C170">
         <v>0</v>
@@ -2366,10 +2366,10 @@
     </row>
     <row r="171" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A171" t="s">
-        <v>13</v>
+        <v>40</v>
       </c>
       <c r="B171" t="s">
-        <v>36</v>
+        <v>18</v>
       </c>
       <c r="C171">
         <v>0</v>
@@ -2377,10 +2377,10 @@
     </row>
     <row r="172" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A172" t="s">
-        <v>13</v>
+        <v>41</v>
       </c>
       <c r="B172" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="C172">
         <v>0</v>
@@ -2388,10 +2388,10 @@
     </row>
     <row r="173" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A173" t="s">
-        <v>13</v>
+        <v>2</v>
       </c>
       <c r="B173" t="s">
-        <v>29</v>
+        <v>18</v>
       </c>
       <c r="C173">
         <v>0</v>
@@ -2399,43 +2399,43 @@
     </row>
     <row r="174" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A174" t="s">
-        <v>13</v>
+        <v>25</v>
       </c>
       <c r="B174" t="s">
-        <v>3</v>
+        <v>18</v>
       </c>
       <c r="C174">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="175" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A175" t="s">
-        <v>13</v>
+        <v>22</v>
       </c>
       <c r="B175" t="s">
-        <v>1</v>
+        <v>18</v>
       </c>
       <c r="C175">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="176" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A176" t="s">
-        <v>31</v>
+        <v>0</v>
       </c>
       <c r="B176" t="s">
-        <v>3</v>
+        <v>18</v>
       </c>
       <c r="C176">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="177" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A177" t="s">
-        <v>31</v>
+        <v>19</v>
       </c>
       <c r="B177" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="C177">
         <v>0</v>
@@ -2443,10 +2443,10 @@
     </row>
     <row r="178" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A178" t="s">
-        <v>31</v>
+        <v>13</v>
       </c>
       <c r="B178" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="C178">
         <v>0</v>
@@ -2457,7 +2457,7 @@
         <v>31</v>
       </c>
       <c r="B179" t="s">
-        <v>11</v>
+        <v>18</v>
       </c>
       <c r="C179">
         <v>0</v>
@@ -2465,10 +2465,10 @@
     </row>
     <row r="180" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A180" t="s">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="B180" t="s">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="C180">
         <v>0</v>
@@ -2476,10 +2476,10 @@
     </row>
     <row r="181" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A181" t="s">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="B181" t="s">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="C181">
         <v>0</v>
@@ -2487,10 +2487,10 @@
     </row>
     <row r="182" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A182" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="B182" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="C182">
         <v>0</v>
@@ -2498,10 +2498,10 @@
     </row>
     <row r="183" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A183" t="s">
-        <v>31</v>
+        <v>5</v>
       </c>
       <c r="B183" t="s">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="C183">
         <v>0</v>
@@ -2509,10 +2509,10 @@
     </row>
     <row r="184" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A184" t="s">
-        <v>31</v>
+        <v>14</v>
       </c>
       <c r="B184" t="s">
-        <v>36</v>
+        <v>18</v>
       </c>
       <c r="C184">
         <v>0</v>
@@ -2520,10 +2520,10 @@
     </row>
     <row r="185" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A185" t="s">
-        <v>31</v>
+        <v>17</v>
       </c>
       <c r="B185" t="s">
-        <v>6</v>
+        <v>18</v>
       </c>
       <c r="C185">
         <v>0</v>
@@ -2531,7 +2531,7 @@
     </row>
     <row r="186" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A186" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="B186" t="s">
         <v>18</v>
@@ -2542,10 +2542,10 @@
     </row>
     <row r="187" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A187" t="s">
-        <v>31</v>
+        <v>8</v>
       </c>
       <c r="B187" t="s">
-        <v>26</v>
+        <v>18</v>
       </c>
       <c r="C187">
         <v>0</v>
@@ -2553,10 +2553,10 @@
     </row>
     <row r="188" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A188" t="s">
-        <v>31</v>
+        <v>7</v>
       </c>
       <c r="B188" t="s">
-        <v>10</v>
+        <v>26</v>
       </c>
       <c r="C188">
         <v>0</v>
@@ -2564,10 +2564,10 @@
     </row>
     <row r="189" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A189" t="s">
-        <v>31</v>
+        <v>38</v>
       </c>
       <c r="B189" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="C189">
         <v>0</v>
@@ -2575,21 +2575,21 @@
     </row>
     <row r="190" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A190" t="s">
-        <v>31</v>
+        <v>40</v>
       </c>
       <c r="B190" t="s">
-        <v>1</v>
+        <v>26</v>
       </c>
       <c r="C190">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="191" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A191" t="s">
-        <v>35</v>
+        <v>25</v>
       </c>
       <c r="B191" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="C191">
         <v>0</v>
@@ -2597,10 +2597,10 @@
     </row>
     <row r="192" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A192" t="s">
-        <v>35</v>
+        <v>22</v>
       </c>
       <c r="B192" t="s">
-        <v>9</v>
+        <v>26</v>
       </c>
       <c r="C192">
         <v>0</v>
@@ -2608,10 +2608,10 @@
     </row>
     <row r="193" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A193" t="s">
-        <v>35</v>
+        <v>0</v>
       </c>
       <c r="B193" t="s">
-        <v>10</v>
+        <v>26</v>
       </c>
       <c r="C193">
         <v>0</v>
@@ -2619,21 +2619,21 @@
     </row>
     <row r="194" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A194" t="s">
-        <v>35</v>
+        <v>19</v>
       </c>
       <c r="B194" t="s">
-        <v>1</v>
+        <v>26</v>
       </c>
       <c r="C194">
-        <v>13</v>
+        <v>0</v>
       </c>
     </row>
     <row r="195" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A195" t="s">
-        <v>35</v>
+        <v>13</v>
       </c>
       <c r="B195" t="s">
-        <v>36</v>
+        <v>26</v>
       </c>
       <c r="C195">
         <v>0</v>
@@ -2641,32 +2641,32 @@
     </row>
     <row r="196" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A196" t="s">
-        <v>35</v>
+        <v>31</v>
       </c>
       <c r="B196" t="s">
-        <v>3</v>
+        <v>26</v>
       </c>
       <c r="C196">
-        <v>14</v>
+        <v>0</v>
       </c>
     </row>
     <row r="197" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A197" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="B197" t="s">
-        <v>42</v>
+        <v>26</v>
       </c>
       <c r="C197">
-        <v>15</v>
+        <v>0</v>
       </c>
     </row>
     <row r="198" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A198" t="s">
-        <v>35</v>
+        <v>27</v>
       </c>
       <c r="B198" t="s">
-        <v>12</v>
+        <v>26</v>
       </c>
       <c r="C198">
         <v>0</v>
@@ -2674,10 +2674,10 @@
     </row>
     <row r="199" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A199" t="s">
-        <v>35</v>
+        <v>28</v>
       </c>
       <c r="B199" t="s">
-        <v>15</v>
+        <v>26</v>
       </c>
       <c r="C199">
         <v>0</v>
@@ -2685,10 +2685,10 @@
     </row>
     <row r="200" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A200" t="s">
-        <v>35</v>
+        <v>14</v>
       </c>
       <c r="B200" t="s">
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="C200">
         <v>0</v>
@@ -2696,10 +2696,10 @@
     </row>
     <row r="201" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A201" t="s">
-        <v>35</v>
+        <v>30</v>
       </c>
       <c r="B201" t="s">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="C201">
         <v>0</v>
@@ -2707,10 +2707,10 @@
     </row>
     <row r="202" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A202" t="s">
-        <v>35</v>
+        <v>17</v>
       </c>
       <c r="B202" t="s">
-        <v>11</v>
+        <v>26</v>
       </c>
       <c r="C202">
         <v>0</v>
@@ -2718,10 +2718,10 @@
     </row>
     <row r="203" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A203" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="B203" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="C203">
         <v>0</v>
@@ -2729,10 +2729,10 @@
     </row>
     <row r="204" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A204" t="s">
-        <v>35</v>
+        <v>8</v>
       </c>
       <c r="B204" t="s">
-        <v>16</v>
+        <v>26</v>
       </c>
       <c r="C204">
         <v>0</v>
@@ -2740,145 +2740,145 @@
     </row>
     <row r="205" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A205" t="s">
-        <v>35</v>
+        <v>7</v>
       </c>
       <c r="B205" t="s">
-        <v>24</v>
+        <v>3</v>
       </c>
       <c r="C205">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="206" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A206" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="B206" t="s">
-        <v>21</v>
+        <v>3</v>
       </c>
       <c r="C206">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="207" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A207" t="s">
-        <v>34</v>
+        <v>4</v>
       </c>
       <c r="B207" t="s">
-        <v>36</v>
+        <v>3</v>
       </c>
       <c r="C207">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="208" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A208" t="s">
-        <v>34</v>
+        <v>40</v>
       </c>
       <c r="B208" t="s">
-        <v>15</v>
+        <v>3</v>
       </c>
       <c r="C208">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="209" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A209" t="s">
-        <v>34</v>
+        <v>41</v>
       </c>
       <c r="B209" t="s">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="C209">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="210" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A210" t="s">
-        <v>34</v>
+        <v>2</v>
       </c>
       <c r="B210" t="s">
-        <v>20</v>
+        <v>3</v>
       </c>
       <c r="C210">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="211" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A211" t="s">
-        <v>34</v>
+        <v>25</v>
       </c>
       <c r="B211" t="s">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="C211">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="212" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A212" t="s">
-        <v>34</v>
+        <v>22</v>
       </c>
       <c r="B212" t="s">
-        <v>23</v>
+        <v>3</v>
       </c>
       <c r="C212">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="213" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A213" t="s">
-        <v>34</v>
+        <v>0</v>
       </c>
       <c r="B213" t="s">
-        <v>18</v>
+        <v>3</v>
       </c>
       <c r="C213">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="214" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A214" t="s">
-        <v>34</v>
+        <v>19</v>
       </c>
       <c r="B214" t="s">
-        <v>26</v>
+        <v>3</v>
       </c>
       <c r="C214">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="215" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A215" t="s">
-        <v>34</v>
+        <v>13</v>
       </c>
       <c r="B215" t="s">
-        <v>16</v>
+        <v>3</v>
       </c>
       <c r="C215">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="216" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A216" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="B216" t="s">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="C216">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="217" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A217" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B217" t="s">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="C217">
-        <v>0</v>
+        <v>14</v>
       </c>
     </row>
     <row r="218" spans="1:3" x14ac:dyDescent="0.3">
@@ -2886,40 +2886,40 @@
         <v>34</v>
       </c>
       <c r="B218" t="s">
-        <v>29</v>
+        <v>3</v>
       </c>
       <c r="C218">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="219" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A219" t="s">
-        <v>34</v>
+        <v>14</v>
       </c>
       <c r="B219" t="s">
-        <v>24</v>
+        <v>3</v>
       </c>
       <c r="C219">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="220" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A220" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="B220" t="s">
         <v>3</v>
       </c>
       <c r="C220">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="221" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A221" t="s">
-        <v>27</v>
+        <v>17</v>
       </c>
       <c r="B221" t="s">
-        <v>24</v>
+        <v>3</v>
       </c>
       <c r="C221">
         <v>2</v>
@@ -2927,32 +2927,32 @@
     </row>
     <row r="222" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A222" t="s">
-        <v>27</v>
+        <v>39</v>
       </c>
       <c r="B222" t="s">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="C222">
-        <v>0</v>
+        <v>36</v>
       </c>
     </row>
     <row r="223" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A223" t="s">
-        <v>27</v>
+        <v>8</v>
       </c>
       <c r="B223" t="s">
-        <v>11</v>
+        <v>3</v>
       </c>
       <c r="C223">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="224" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A224" t="s">
-        <v>27</v>
+        <v>39</v>
       </c>
       <c r="B224" t="s">
-        <v>23</v>
+        <v>43</v>
       </c>
       <c r="C224">
         <v>0</v>
@@ -2960,10 +2960,10 @@
     </row>
     <row r="225" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A225" t="s">
-        <v>27</v>
+        <v>33</v>
       </c>
       <c r="B225" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="C225">
         <v>0</v>
@@ -2971,10 +2971,10 @@
     </row>
     <row r="226" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A226" t="s">
-        <v>27</v>
+        <v>7</v>
       </c>
       <c r="B226" t="s">
-        <v>26</v>
+        <v>16</v>
       </c>
       <c r="C226">
         <v>0</v>
@@ -2982,7 +2982,7 @@
     </row>
     <row r="227" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A227" t="s">
-        <v>27</v>
+        <v>38</v>
       </c>
       <c r="B227" t="s">
         <v>16</v>
@@ -2993,10 +2993,10 @@
     </row>
     <row r="228" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A228" t="s">
-        <v>27</v>
+        <v>4</v>
       </c>
       <c r="B228" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="C228">
         <v>0</v>
@@ -3004,10 +3004,10 @@
     </row>
     <row r="229" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A229" t="s">
-        <v>27</v>
+        <v>41</v>
       </c>
       <c r="B229" t="s">
-        <v>36</v>
+        <v>16</v>
       </c>
       <c r="C229">
         <v>0</v>
@@ -3015,10 +3015,10 @@
     </row>
     <row r="230" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A230" t="s">
-        <v>27</v>
+        <v>2</v>
       </c>
       <c r="B230" t="s">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="C230">
         <v>0</v>
@@ -3026,10 +3026,10 @@
     </row>
     <row r="231" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A231" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="B231" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="C231">
         <v>0</v>
@@ -3037,10 +3037,10 @@
     </row>
     <row r="232" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A232" t="s">
-        <v>27</v>
+        <v>22</v>
       </c>
       <c r="B232" t="s">
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="C232">
         <v>0</v>
@@ -3048,10 +3048,10 @@
     </row>
     <row r="233" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A233" t="s">
-        <v>27</v>
+        <v>0</v>
       </c>
       <c r="B233" t="s">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="C233">
         <v>0</v>
@@ -3059,10 +3059,10 @@
     </row>
     <row r="234" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A234" t="s">
-        <v>27</v>
+        <v>19</v>
       </c>
       <c r="B234" t="s">
-        <v>29</v>
+        <v>16</v>
       </c>
       <c r="C234">
         <v>0</v>
@@ -3070,43 +3070,43 @@
     </row>
     <row r="235" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A235" t="s">
-        <v>27</v>
+        <v>13</v>
       </c>
       <c r="B235" t="s">
-        <v>1</v>
+        <v>16</v>
       </c>
       <c r="C235">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="236" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A236" t="s">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="B236" t="s">
-        <v>6</v>
+        <v>16</v>
       </c>
       <c r="C236">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="237" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A237" t="s">
-        <v>28</v>
+        <v>35</v>
       </c>
       <c r="B237" t="s">
-        <v>24</v>
+        <v>16</v>
       </c>
       <c r="C237">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="238" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A238" t="s">
-        <v>28</v>
+        <v>34</v>
       </c>
       <c r="B238" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C238">
         <v>0</v>
@@ -3114,10 +3114,10 @@
     </row>
     <row r="239" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A239" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B239" t="s">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="C239">
         <v>0</v>
@@ -3128,7 +3128,7 @@
         <v>28</v>
       </c>
       <c r="B240" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="C240">
         <v>0</v>
@@ -3136,10 +3136,10 @@
     </row>
     <row r="241" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A241" t="s">
-        <v>28</v>
+        <v>5</v>
       </c>
       <c r="B241" t="s">
-        <v>23</v>
+        <v>16</v>
       </c>
       <c r="C241">
         <v>0</v>
@@ -3147,10 +3147,10 @@
     </row>
     <row r="242" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A242" t="s">
-        <v>28</v>
+        <v>14</v>
       </c>
       <c r="B242" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="C242">
         <v>0</v>
@@ -3158,10 +3158,10 @@
     </row>
     <row r="243" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A243" t="s">
-        <v>28</v>
+        <v>17</v>
       </c>
       <c r="B243" t="s">
-        <v>26</v>
+        <v>16</v>
       </c>
       <c r="C243">
         <v>0</v>
@@ -3169,10 +3169,10 @@
     </row>
     <row r="244" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A244" t="s">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="B244" t="s">
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="C244">
         <v>0</v>
@@ -3180,32 +3180,32 @@
     </row>
     <row r="245" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A245" t="s">
-        <v>28</v>
+        <v>39</v>
       </c>
       <c r="B245" t="s">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="C245">
-        <v>0</v>
+        <v>33</v>
       </c>
     </row>
     <row r="246" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A246" t="s">
-        <v>28</v>
+        <v>33</v>
       </c>
       <c r="B246" t="s">
-        <v>29</v>
+        <v>24</v>
       </c>
       <c r="C246">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="247" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A247" t="s">
-        <v>28</v>
+        <v>7</v>
       </c>
       <c r="B247" t="s">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="C247">
         <v>0</v>
@@ -3213,10 +3213,10 @@
     </row>
     <row r="248" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A248" t="s">
-        <v>28</v>
+        <v>38</v>
       </c>
       <c r="B248" t="s">
-        <v>16</v>
+        <v>24</v>
       </c>
       <c r="C248">
         <v>0</v>
@@ -3224,10 +3224,10 @@
     </row>
     <row r="249" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A249" t="s">
-        <v>28</v>
+        <v>4</v>
       </c>
       <c r="B249" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="C249">
         <v>0</v>
@@ -3235,10 +3235,10 @@
     </row>
     <row r="250" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A250" t="s">
-        <v>28</v>
+        <v>40</v>
       </c>
       <c r="B250" t="s">
-        <v>36</v>
+        <v>24</v>
       </c>
       <c r="C250">
         <v>0</v>
@@ -3246,21 +3246,21 @@
     </row>
     <row r="251" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A251" t="s">
-        <v>5</v>
+        <v>41</v>
       </c>
       <c r="B251" t="s">
-        <v>6</v>
+        <v>24</v>
       </c>
       <c r="C251">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="252" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A252" t="s">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="B252" t="s">
-        <v>11</v>
+        <v>24</v>
       </c>
       <c r="C252">
         <v>0</v>
@@ -3268,10 +3268,10 @@
     </row>
     <row r="253" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A253" t="s">
-        <v>5</v>
+        <v>22</v>
       </c>
       <c r="B253" t="s">
-        <v>12</v>
+        <v>24</v>
       </c>
       <c r="C253">
         <v>0</v>
@@ -3279,10 +3279,10 @@
     </row>
     <row r="254" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A254" t="s">
-        <v>5</v>
+        <v>19</v>
       </c>
       <c r="B254" t="s">
-        <v>9</v>
+        <v>24</v>
       </c>
       <c r="C254">
         <v>0</v>
@@ -3290,10 +3290,10 @@
     </row>
     <row r="255" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A255" t="s">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="B255" t="s">
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="C255">
         <v>0</v>
@@ -3301,21 +3301,21 @@
     </row>
     <row r="256" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A256" t="s">
-        <v>5</v>
+        <v>31</v>
       </c>
       <c r="B256" t="s">
-        <v>1</v>
+        <v>24</v>
       </c>
       <c r="C256">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="257" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A257" t="s">
-        <v>5</v>
+        <v>35</v>
       </c>
       <c r="B257" t="s">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="C257">
         <v>0</v>
@@ -3323,54 +3323,54 @@
     </row>
     <row r="258" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A258" t="s">
-        <v>5</v>
+        <v>34</v>
       </c>
       <c r="B258" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="C258">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="259" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A259" t="s">
-        <v>5</v>
+        <v>27</v>
       </c>
       <c r="B259" t="s">
-        <v>10</v>
+        <v>24</v>
       </c>
       <c r="C259">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="260" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A260" t="s">
-        <v>5</v>
+        <v>28</v>
       </c>
       <c r="B260" t="s">
-        <v>36</v>
+        <v>24</v>
       </c>
       <c r="C260">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="261" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A261" t="s">
-        <v>5</v>
+        <v>14</v>
       </c>
       <c r="B261" t="s">
-        <v>16</v>
+        <v>24</v>
       </c>
       <c r="C261">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="262" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A262" t="s">
-        <v>5</v>
+        <v>30</v>
       </c>
       <c r="B262" t="s">
-        <v>29</v>
+        <v>24</v>
       </c>
       <c r="C262">
         <v>0</v>
@@ -3378,10 +3378,10 @@
     </row>
     <row r="263" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A263" t="s">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="B263" t="s">
-        <v>15</v>
+        <v>24</v>
       </c>
       <c r="C263">
         <v>0</v>
@@ -3389,21 +3389,21 @@
     </row>
     <row r="264" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A264" t="s">
-        <v>14</v>
+        <v>33</v>
       </c>
       <c r="B264" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="C264">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="265" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A265" t="s">
-        <v>14</v>
+        <v>7</v>
       </c>
       <c r="B265" t="s">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="C265">
         <v>0</v>
@@ -3411,21 +3411,21 @@
     </row>
     <row r="266" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A266" t="s">
-        <v>14</v>
+        <v>38</v>
       </c>
       <c r="B266" t="s">
-        <v>24</v>
+        <v>9</v>
       </c>
       <c r="C266">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="267" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A267" t="s">
-        <v>14</v>
+        <v>4</v>
       </c>
       <c r="B267" t="s">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="C267">
         <v>0</v>
@@ -3433,10 +3433,10 @@
     </row>
     <row r="268" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A268" t="s">
-        <v>14</v>
+        <v>40</v>
       </c>
       <c r="B268" t="s">
-        <v>20</v>
+        <v>9</v>
       </c>
       <c r="C268">
         <v>0</v>
@@ -3444,10 +3444,10 @@
     </row>
     <row r="269" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A269" t="s">
-        <v>14</v>
+        <v>41</v>
       </c>
       <c r="B269" t="s">
-        <v>23</v>
+        <v>9</v>
       </c>
       <c r="C269">
         <v>0</v>
@@ -3455,10 +3455,10 @@
     </row>
     <row r="270" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A270" t="s">
-        <v>14</v>
+        <v>2</v>
       </c>
       <c r="B270" t="s">
-        <v>18</v>
+        <v>9</v>
       </c>
       <c r="C270">
         <v>0</v>
@@ -3466,10 +3466,10 @@
     </row>
     <row r="271" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A271" t="s">
-        <v>14</v>
+        <v>25</v>
       </c>
       <c r="B271" t="s">
-        <v>26</v>
+        <v>9</v>
       </c>
       <c r="C271">
         <v>0</v>
@@ -3477,10 +3477,10 @@
     </row>
     <row r="272" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A272" t="s">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="B272" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C272">
         <v>0</v>
@@ -3488,10 +3488,10 @@
     </row>
     <row r="273" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A273" t="s">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="B273" t="s">
-        <v>29</v>
+        <v>9</v>
       </c>
       <c r="C273">
         <v>0</v>
@@ -3499,10 +3499,10 @@
     </row>
     <row r="274" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A274" t="s">
-        <v>14</v>
+        <v>35</v>
       </c>
       <c r="B274" t="s">
-        <v>21</v>
+        <v>9</v>
       </c>
       <c r="C274">
         <v>0</v>
@@ -3510,18 +3510,18 @@
     </row>
     <row r="275" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A275" t="s">
-        <v>14</v>
+        <v>34</v>
       </c>
       <c r="B275" t="s">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="C275">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="276" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A276" t="s">
-        <v>14</v>
+        <v>27</v>
       </c>
       <c r="B276" t="s">
         <v>9</v>
@@ -3532,10 +3532,10 @@
     </row>
     <row r="277" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A277" t="s">
-        <v>14</v>
+        <v>28</v>
       </c>
       <c r="B277" t="s">
-        <v>36</v>
+        <v>9</v>
       </c>
       <c r="C277">
         <v>0</v>
@@ -3543,10 +3543,10 @@
     </row>
     <row r="278" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A278" t="s">
-        <v>37</v>
+        <v>5</v>
       </c>
       <c r="B278" t="s">
-        <v>36</v>
+        <v>9</v>
       </c>
       <c r="C278">
         <v>0</v>
@@ -3554,10 +3554,10 @@
     </row>
     <row r="279" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A279" t="s">
-        <v>37</v>
+        <v>14</v>
       </c>
       <c r="B279" t="s">
-        <v>42</v>
+        <v>9</v>
       </c>
       <c r="C279">
         <v>0</v>
@@ -3568,29 +3568,29 @@
         <v>30</v>
       </c>
       <c r="B280" t="s">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="C280">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="281" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A281" t="s">
-        <v>30</v>
+        <v>17</v>
       </c>
       <c r="B281" t="s">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="C281">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="282" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A282" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="B282" t="s">
-        <v>20</v>
+        <v>9</v>
       </c>
       <c r="C282">
         <v>0</v>
@@ -3598,21 +3598,21 @@
     </row>
     <row r="283" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A283" t="s">
-        <v>30</v>
+        <v>39</v>
       </c>
       <c r="B283" t="s">
-        <v>21</v>
+        <v>9</v>
       </c>
       <c r="C283">
-        <v>0</v>
+        <v>38</v>
       </c>
     </row>
     <row r="284" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A284" t="s">
-        <v>30</v>
+        <v>8</v>
       </c>
       <c r="B284" t="s">
-        <v>23</v>
+        <v>9</v>
       </c>
       <c r="C284">
         <v>0</v>
@@ -3620,10 +3620,10 @@
     </row>
     <row r="285" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A285" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="B285" t="s">
-        <v>36</v>
+        <v>10</v>
       </c>
       <c r="C285">
         <v>0</v>
@@ -3631,10 +3631,10 @@
     </row>
     <row r="286" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A286" t="s">
-        <v>30</v>
+        <v>7</v>
       </c>
       <c r="B286" t="s">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="C286">
         <v>0</v>
@@ -3642,10 +3642,10 @@
     </row>
     <row r="287" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A287" t="s">
-        <v>30</v>
+        <v>38</v>
       </c>
       <c r="B287" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="C287">
         <v>0</v>
@@ -3653,10 +3653,10 @@
     </row>
     <row r="288" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A288" t="s">
-        <v>30</v>
+        <v>4</v>
       </c>
       <c r="B288" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C288">
         <v>0</v>
@@ -3664,10 +3664,10 @@
     </row>
     <row r="289" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A289" t="s">
-        <v>30</v>
+        <v>40</v>
       </c>
       <c r="B289" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="C289">
         <v>0</v>
@@ -3675,10 +3675,10 @@
     </row>
     <row r="290" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A290" t="s">
-        <v>30</v>
+        <v>2</v>
       </c>
       <c r="B290" t="s">
-        <v>26</v>
+        <v>10</v>
       </c>
       <c r="C290">
         <v>0</v>
@@ -3686,10 +3686,10 @@
     </row>
     <row r="291" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A291" t="s">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="B291" t="s">
-        <v>24</v>
+        <v>10</v>
       </c>
       <c r="C291">
         <v>0</v>
@@ -3697,10 +3697,10 @@
     </row>
     <row r="292" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A292" t="s">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="B292" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C292">
         <v>0</v>
@@ -3708,7 +3708,7 @@
     </row>
     <row r="293" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A293" t="s">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="B293" t="s">
         <v>10</v>
@@ -3719,10 +3719,10 @@
     </row>
     <row r="294" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A294" t="s">
-        <v>30</v>
+        <v>19</v>
       </c>
       <c r="B294" t="s">
-        <v>29</v>
+        <v>10</v>
       </c>
       <c r="C294">
         <v>0</v>
@@ -3730,32 +3730,32 @@
     </row>
     <row r="295" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A295" t="s">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="B295" t="s">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="C295">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="296" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A296" t="s">
-        <v>17</v>
+        <v>31</v>
       </c>
       <c r="B296" t="s">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="C296">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="297" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A297" t="s">
-        <v>17</v>
+        <v>35</v>
       </c>
       <c r="B297" t="s">
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="C297">
         <v>0</v>
@@ -3763,10 +3763,10 @@
     </row>
     <row r="298" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A298" t="s">
-        <v>17</v>
+        <v>34</v>
       </c>
       <c r="B298" t="s">
-        <v>26</v>
+        <v>10</v>
       </c>
       <c r="C298">
         <v>0</v>
@@ -3774,10 +3774,10 @@
     </row>
     <row r="299" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A299" t="s">
-        <v>17</v>
+        <v>27</v>
       </c>
       <c r="B299" t="s">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="C299">
         <v>0</v>
@@ -3785,10 +3785,10 @@
     </row>
     <row r="300" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A300" t="s">
-        <v>17</v>
+        <v>28</v>
       </c>
       <c r="B300" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C300">
         <v>0</v>
@@ -3796,7 +3796,7 @@
     </row>
     <row r="301" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A301" t="s">
-        <v>17</v>
+        <v>5</v>
       </c>
       <c r="B301" t="s">
         <v>10</v>
@@ -3807,10 +3807,10 @@
     </row>
     <row r="302" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A302" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="B302" t="s">
-        <v>29</v>
+        <v>10</v>
       </c>
       <c r="C302">
         <v>0</v>
@@ -3818,10 +3818,10 @@
     </row>
     <row r="303" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A303" t="s">
-        <v>17</v>
+        <v>30</v>
       </c>
       <c r="B303" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C303">
         <v>0</v>
@@ -3832,7 +3832,7 @@
         <v>17</v>
       </c>
       <c r="B304" t="s">
-        <v>36</v>
+        <v>10</v>
       </c>
       <c r="C304">
         <v>0</v>
@@ -3840,10 +3840,10 @@
     </row>
     <row r="305" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A305" t="s">
-        <v>17</v>
+        <v>32</v>
       </c>
       <c r="B305" t="s">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="C305">
         <v>0</v>
@@ -3851,10 +3851,10 @@
     </row>
     <row r="306" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A306" t="s">
-        <v>17</v>
+        <v>8</v>
       </c>
       <c r="B306" t="s">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="C306">
         <v>0</v>
@@ -3862,10 +3862,10 @@
     </row>
     <row r="307" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A307" t="s">
-        <v>17</v>
+        <v>33</v>
       </c>
       <c r="B307" t="s">
-        <v>21</v>
+        <v>29</v>
       </c>
       <c r="C307">
         <v>0</v>
@@ -3873,10 +3873,10 @@
     </row>
     <row r="308" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A308" t="s">
-        <v>17</v>
+        <v>7</v>
       </c>
       <c r="B308" t="s">
-        <v>12</v>
+        <v>29</v>
       </c>
       <c r="C308">
         <v>0</v>
@@ -3884,10 +3884,10 @@
     </row>
     <row r="309" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A309" t="s">
-        <v>17</v>
+        <v>38</v>
       </c>
       <c r="B309" t="s">
-        <v>23</v>
+        <v>29</v>
       </c>
       <c r="C309">
         <v>0</v>
@@ -3895,21 +3895,21 @@
     </row>
     <row r="310" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A310" t="s">
-        <v>32</v>
+        <v>4</v>
       </c>
       <c r="B310" t="s">
-        <v>6</v>
+        <v>29</v>
       </c>
       <c r="C310">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="311" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A311" t="s">
-        <v>32</v>
+        <v>40</v>
       </c>
       <c r="B311" t="s">
-        <v>15</v>
+        <v>29</v>
       </c>
       <c r="C311">
         <v>0</v>
@@ -3917,10 +3917,10 @@
     </row>
     <row r="312" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A312" t="s">
-        <v>32</v>
+        <v>41</v>
       </c>
       <c r="B312" t="s">
-        <v>20</v>
+        <v>29</v>
       </c>
       <c r="C312">
         <v>0</v>
@@ -3928,10 +3928,10 @@
     </row>
     <row r="313" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A313" t="s">
-        <v>32</v>
+        <v>2</v>
       </c>
       <c r="B313" t="s">
-        <v>21</v>
+        <v>29</v>
       </c>
       <c r="C313">
         <v>0</v>
@@ -3939,10 +3939,10 @@
     </row>
     <row r="314" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A314" t="s">
-        <v>32</v>
+        <v>25</v>
       </c>
       <c r="B314" t="s">
-        <v>11</v>
+        <v>29</v>
       </c>
       <c r="C314">
         <v>0</v>
@@ -3950,10 +3950,10 @@
     </row>
     <row r="315" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A315" t="s">
-        <v>32</v>
+        <v>22</v>
       </c>
       <c r="B315" t="s">
-        <v>12</v>
+        <v>29</v>
       </c>
       <c r="C315">
         <v>0</v>
@@ -3961,10 +3961,10 @@
     </row>
     <row r="316" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A316" t="s">
-        <v>32</v>
+        <v>0</v>
       </c>
       <c r="B316" t="s">
-        <v>23</v>
+        <v>29</v>
       </c>
       <c r="C316">
         <v>0</v>
@@ -3972,10 +3972,10 @@
     </row>
     <row r="317" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A317" t="s">
-        <v>32</v>
+        <v>13</v>
       </c>
       <c r="B317" t="s">
-        <v>18</v>
+        <v>29</v>
       </c>
       <c r="C317">
         <v>0</v>
@@ -3983,10 +3983,10 @@
     </row>
     <row r="318" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A318" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B318" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="C318">
         <v>0</v>
@@ -3994,10 +3994,10 @@
     </row>
     <row r="319" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A319" t="s">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="B319" t="s">
-        <v>36</v>
+        <v>29</v>
       </c>
       <c r="C319">
         <v>0</v>
@@ -4005,10 +4005,10 @@
     </row>
     <row r="320" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A320" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="B320" t="s">
-        <v>16</v>
+        <v>29</v>
       </c>
       <c r="C320">
         <v>0</v>
@@ -4016,10 +4016,10 @@
     </row>
     <row r="321" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A321" t="s">
-        <v>32</v>
+        <v>27</v>
       </c>
       <c r="B321" t="s">
-        <v>9</v>
+        <v>29</v>
       </c>
       <c r="C321">
         <v>0</v>
@@ -4027,10 +4027,10 @@
     </row>
     <row r="322" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A322" t="s">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="B322" t="s">
-        <v>10</v>
+        <v>29</v>
       </c>
       <c r="C322">
         <v>0</v>
@@ -4038,7 +4038,7 @@
     </row>
     <row r="323" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A323" t="s">
-        <v>32</v>
+        <v>5</v>
       </c>
       <c r="B323" t="s">
         <v>29</v>
@@ -4049,266 +4049,266 @@
     </row>
     <row r="324" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A324" t="s">
-        <v>32</v>
+        <v>14</v>
       </c>
       <c r="B324" t="s">
-        <v>1</v>
+        <v>29</v>
       </c>
       <c r="C324">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="325" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A325" t="s">
-        <v>39</v>
+        <v>30</v>
       </c>
       <c r="B325" t="s">
-        <v>20</v>
+        <v>29</v>
       </c>
       <c r="C325">
-        <v>37</v>
+        <v>0</v>
       </c>
     </row>
     <row r="326" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A326" t="s">
-        <v>39</v>
+        <v>17</v>
       </c>
       <c r="B326" t="s">
-        <v>11</v>
+        <v>29</v>
       </c>
       <c r="C326">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="327" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A327" t="s">
-        <v>39</v>
+        <v>32</v>
       </c>
       <c r="B327" t="s">
-        <v>12</v>
+        <v>29</v>
       </c>
       <c r="C327">
-        <v>39</v>
+        <v>0</v>
       </c>
     </row>
     <row r="328" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A328" t="s">
-        <v>39</v>
+        <v>8</v>
       </c>
       <c r="B328" t="s">
-        <v>3</v>
+        <v>29</v>
       </c>
       <c r="C328">
-        <v>36</v>
+        <v>0</v>
       </c>
     </row>
     <row r="329" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A329" t="s">
-        <v>39</v>
+        <v>7</v>
       </c>
       <c r="B329" t="s">
-        <v>16</v>
+        <v>1</v>
       </c>
       <c r="C329">
-        <v>33</v>
+        <v>3</v>
       </c>
     </row>
     <row r="330" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A330" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B330" t="s">
         <v>1</v>
       </c>
       <c r="C330">
-        <v>35</v>
+        <v>3</v>
       </c>
     </row>
     <row r="331" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A331" t="s">
-        <v>39</v>
+        <v>4</v>
       </c>
       <c r="B331" t="s">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="C331">
-        <v>38</v>
+        <v>3</v>
       </c>
     </row>
     <row r="332" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A332" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="B332" t="s">
-        <v>36</v>
+        <v>1</v>
       </c>
       <c r="C332">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="333" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A333" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="B333" t="s">
-        <v>43</v>
+        <v>1</v>
       </c>
       <c r="C333">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="334" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A334" t="s">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="B334" t="s">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="C334">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="335" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A335" t="s">
-        <v>8</v>
+        <v>25</v>
       </c>
       <c r="B335" t="s">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="C335">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="336" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A336" t="s">
-        <v>8</v>
+        <v>22</v>
       </c>
       <c r="B336" t="s">
+        <v>1</v>
+      </c>
+      <c r="C336">
         <v>3</v>
-      </c>
-      <c r="C336">
-        <v>2</v>
       </c>
     </row>
     <row r="337" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A337" t="s">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="B337" t="s">
-        <v>15</v>
+        <v>1</v>
       </c>
       <c r="C337">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="338" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A338" t="s">
-        <v>8</v>
+        <v>19</v>
       </c>
       <c r="B338" t="s">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="C338">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="339" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A339" t="s">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="B339" t="s">
-        <v>20</v>
+        <v>1</v>
       </c>
       <c r="C339">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="340" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A340" t="s">
-        <v>8</v>
+        <v>31</v>
       </c>
       <c r="B340" t="s">
-        <v>21</v>
+        <v>1</v>
       </c>
       <c r="C340">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="341" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A341" t="s">
-        <v>8</v>
+        <v>35</v>
       </c>
       <c r="B341" t="s">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="C341">
-        <v>0</v>
+        <v>13</v>
       </c>
     </row>
     <row r="342" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A342" t="s">
-        <v>8</v>
+        <v>27</v>
       </c>
       <c r="B342" t="s">
-        <v>18</v>
+        <v>1</v>
       </c>
       <c r="C342">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="343" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A343" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="B343" t="s">
-        <v>26</v>
+        <v>1</v>
       </c>
       <c r="C343">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="344" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A344" t="s">
-        <v>8</v>
+        <v>30</v>
       </c>
       <c r="B344" t="s">
-        <v>24</v>
+        <v>1</v>
       </c>
       <c r="C344">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="345" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A345" t="s">
-        <v>8</v>
+        <v>17</v>
       </c>
       <c r="B345" t="s">
-        <v>23</v>
+        <v>1</v>
       </c>
       <c r="C345">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="346" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A346" t="s">
-        <v>8</v>
+        <v>32</v>
       </c>
       <c r="B346" t="s">
-        <v>36</v>
+        <v>1</v>
       </c>
       <c r="C346">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="347" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A347" t="s">
-        <v>8</v>
+        <v>39</v>
       </c>
       <c r="B347" t="s">
-        <v>29</v>
+        <v>1</v>
       </c>
       <c r="C347">
-        <v>0</v>
+        <v>35</v>
       </c>
     </row>
     <row r="348" spans="1:3" x14ac:dyDescent="0.3">
@@ -4325,7 +4325,7 @@
   </sheetData>
   <autoFilter ref="A1:C348" xr:uid="{00000000-0001-0000-0000-000000000000}">
     <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:C348">
-      <sortCondition ref="A1:A348"/>
+      <sortCondition ref="B1:B348"/>
     </sortState>
   </autoFilter>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
